--- a/Constant.xlsx
+++ b/Constant.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="134">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -222,6 +222,114 @@
     <t xml:space="preserve">OWNER_ROUTE</t>
   </si>
   <si>
+    <t xml:space="preserve">LIMITS_MAX_ROUTES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIMITS_MAX_STEPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TimeoutMs_Noria_Start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TimeoutMs_Noria_SpeedPause</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TimeoutMs_Gate_Move</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TimeoutMs_Gate_Position_Unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAN_REJ_OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAN_REJ_SLOT_UNMAPPED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAN_REJ_LOCAL_MANUAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAN_REJ_NOT_ENABLED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAN_REJ_OWNER_BUSY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAN_REJ_CMD_INVALID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAN_REJ_ARBITER_FAIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLT_NO_FEEDBACK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLT_ALINGMENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLT_GATE_MOVE_TIMEOUT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLT_GATE_POS_UNKNOWN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLT_BOTH_SENSORS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMD_GATE_OPEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMD_GATE_CLOSED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TimeoutMs_Fan_Feedback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAN_REJ_NOT_IDLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMD_SET_FORCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMD_RELEASE_OWNER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMD_START</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMD_STOP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMD_RESET</t>
+  </si>
+  <si>
     <t xml:space="preserve">ROUTE_STS_IDLE</t>
   </si>
   <si>
@@ -231,45 +339,24 @@
     <t xml:space="preserve">ROUTE_STS_LOCKING</t>
   </si>
   <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
     <t xml:space="preserve">ROUTE_STS_STARTING</t>
   </si>
   <si>
-    <t xml:space="preserve">30</t>
-  </si>
-  <si>
     <t xml:space="preserve">ROUTE_STS_RUNNING</t>
   </si>
   <si>
-    <t xml:space="preserve">40</t>
-  </si>
-  <si>
     <t xml:space="preserve">ROUTE_STS_STOPPING</t>
   </si>
   <si>
-    <t xml:space="preserve">50</t>
-  </si>
-  <si>
     <t xml:space="preserve">ROUTE_STS_DONE</t>
   </si>
   <si>
-    <t xml:space="preserve">1000</t>
-  </si>
-  <si>
     <t xml:space="preserve">ROUTE_STS_REJECTED</t>
   </si>
   <si>
-    <t xml:space="preserve">1100</t>
-  </si>
-  <si>
     <t xml:space="preserve">ROUTE_STS_ABORTED</t>
   </si>
   <si>
-    <t xml:space="preserve">1200</t>
-  </si>
-  <si>
     <t xml:space="preserve">RT_CMD_NONE</t>
   </si>
   <si>
@@ -279,9 +366,6 @@
     <t xml:space="preserve">RT_CMD_STOP_OP</t>
   </si>
   <si>
-    <t xml:space="preserve">RT_CMD_STOP_SAFE</t>
-  </si>
-  <si>
     <t xml:space="preserve">RS_ACT_START</t>
   </si>
   <si>
@@ -303,184 +387,37 @@
     <t xml:space="preserve">STEP_STS_DONE</t>
   </si>
   <si>
-    <t xml:space="preserve">STEP_STS_TIMEOUT</t>
+    <t xml:space="preserve">ROUTE_REJ_BY_CONTRACT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUTE_REJ_BY_OWNER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUTE_REJ_NOT_READY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUTE_REJ_DUPLICATE_START</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUTE_REJ_BY_SAFETY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUTE_ABRT_BY_OPERATOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUTE_ABRT_BY_LOCAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUTE_ABRT_BY_FAULT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUTE_ABRT_BY_SAFETY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUTE_ABRT_BY_OWNER</t>
   </si>
   <si>
     <t xml:space="preserve">ROUTE_DONE_OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUTE_REJ_BY_SAFETY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUTE_REJ_BY_OWNER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUTE_REJ_BY_CONTRACT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUTE_REJ_NOT_READY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUTE_REJ_DUPLICATE_START</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUTE_ABRT_BY_OPERATOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUTE_ABRT_BY_SAFETY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUTE_ABRT_BY_LOCAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUTE_ABRT_BY_FAULT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUTE_ABRT_STARTING_FAILED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUTE_ABRT_BY_OWNER </t>
-  </si>
-  <si>
-    <t xml:space="preserve">205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIMITS_MAX_ROUTES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIMITS_MAX_STEPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TimeoutMs_Noria_Start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TimeoutMs_Noria_SpeedPause</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TimeoutMs_Gate_Move</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TimeoutMs_Gate_Position_Unknown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAN_REJ_OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAN_REJ_SLOT_UNMAPPED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAN_REJ_LOCAL_MANUAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAN_REJ_NOT_ENABLED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAN_REJ_OWNER_BUSY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAN_REJ_CMD_INVALID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAN_REJ_ARBITER_FAIL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLT_NO_FEEDBACK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLT_ALINGMENT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLT_GATE_MOVE_TIMEOUT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLT_GATE_POS_UNKNOWN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLT_BOTH_SENSORS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CMD_GATE_OPEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CMD_GATE_CLOSED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TimeoutMs_Fan_Feedback</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAN_REJ_NOT_IDLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CMD_SET_FORCE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CMD_RELEASE_OWNER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CMD_START</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CMD_STOP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CMD_RESET</t>
   </si>
   <si>
     <t xml:space="preserve">BelongsToUnit</t>
@@ -569,12 +506,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -907,10 +844,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E85"/>
+  <dimension ref="A1:E82"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="35.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="35.77"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1298,10 +1235,10 @@
         <v>11</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E26" s="1"/>
     </row>
@@ -1313,25 +1250,25 @@
         <v>11</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="E27" s="1"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="E28" s="1"/>
     </row>
@@ -1343,91 +1280,91 @@
         <v>11</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="E29" s="1"/>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="E30" s="1"/>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E31" s="1"/>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="E32" s="1"/>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="E33" s="1"/>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="E34" s="1"/>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>11</v>
@@ -1436,13 +1373,13 @@
         <v>29</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="E35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>11</v>
@@ -1451,13 +1388,13 @@
         <v>29</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E36" s="1"/>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>11</v>
@@ -1466,13 +1403,13 @@
         <v>29</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E37" s="1"/>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>11</v>
@@ -1481,67 +1418,67 @@
         <v>29</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="E38" s="1"/>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="E39" s="1"/>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="E40" s="1"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="E41" s="1"/>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="E42" s="1"/>
     </row>
@@ -1553,16 +1490,16 @@
         <v>11</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="E43" s="1"/>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>11</v>
@@ -1571,13 +1508,13 @@
         <v>29</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E44" s="1"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>11</v>
@@ -1586,67 +1523,67 @@
         <v>29</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E45" s="1"/>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E46" s="1"/>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="E47" s="1"/>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>96</v>
+        <v>49</v>
       </c>
       <c r="E48" s="1"/>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="E49" s="1"/>
     </row>
@@ -1658,537 +1595,462 @@
         <v>11</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>100</v>
+        <v>43</v>
       </c>
       <c r="E50" s="1"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>102</v>
+        <v>45</v>
       </c>
       <c r="E51" s="1"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E52" s="1"/>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B53" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C53" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D53" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D52" s="1" t="s">
+      <c r="B54" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D54" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E52" s="1"/>
-    </row>
-    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="s">
+      <c r="B55" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C55" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D55" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D53" s="1" t="s">
+      <c r="B56" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C56" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D56" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="E53" s="1"/>
-    </row>
-    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="s">
+      <c r="B57" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C57" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D57" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D54" s="1" t="s">
+      <c r="B58" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D58" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E54" s="1"/>
-    </row>
-    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="s">
+      <c r="B59" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C59" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D59" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D55" s="1" t="s">
+      <c r="B60" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D60" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E55" s="1"/>
-    </row>
-    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="s">
+      <c r="B61" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C61" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D61" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D56" s="1" t="s">
+      <c r="B62" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="D62" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="E56" s="1"/>
-    </row>
-    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="s">
+      <c r="B63" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="D63" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D57" s="1" t="s">
+      <c r="B64" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="D64" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="E57" s="1"/>
-    </row>
-    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2" t="s">
+      <c r="B65" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C65" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="D65" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D58" s="1" t="s">
+      <c r="B66" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C66" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="D66" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E58" s="1"/>
-    </row>
-    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="s">
+      <c r="B67" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C67" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="D67" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E59" s="1"/>
-    </row>
-    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="s">
+      <c r="B68" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C68" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="D68" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D60" s="1" t="s">
+      <c r="B69" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="D69" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E60" s="1"/>
-    </row>
-    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="s">
+      <c r="B70" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="D70" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E61" s="1"/>
-    </row>
-    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="s">
+      <c r="B71" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C71" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="D71" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E62" s="1"/>
-    </row>
-    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="s">
+      <c r="B72" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D72" s="0" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D63" s="1" t="s">
+      <c r="B73" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C73" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D73" s="0" t="n">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="E63" s="1"/>
-    </row>
-    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="s">
+      <c r="B74" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C74" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D74" s="0" t="n">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E64" s="1"/>
-    </row>
-    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="s">
+      <c r="B75" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C75" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D75" s="0" t="n">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E65" s="1"/>
-    </row>
-    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="1" t="s">
+      <c r="B76" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C76" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D76" s="0" t="n">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E66" s="1"/>
-    </row>
-    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="s">
+      <c r="B77" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C77" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D77" s="0" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E67" s="1"/>
-    </row>
-    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1" t="s">
+      <c r="B78" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C78" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D78" s="0" t="n">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E68" s="1"/>
-    </row>
-    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1" t="s">
+      <c r="B79" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C79" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D79" s="0" t="n">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E69" s="1"/>
-    </row>
-    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1" t="s">
+      <c r="B80" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C80" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D80" s="0" t="n">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E70" s="1"/>
-    </row>
-    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="s">
+      <c r="B81" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C81" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D81" s="0" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E71" s="1"/>
-    </row>
-    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E72" s="1"/>
-    </row>
-    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E73" s="1"/>
-    </row>
-    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="E74" s="1"/>
-    </row>
-    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="E75" s="1"/>
-    </row>
-    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="E76" s="1"/>
-    </row>
-    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E77" s="1"/>
-    </row>
-    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E78" s="1"/>
-    </row>
-    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E79" s="1"/>
-    </row>
-    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="E80" s="1"/>
-    </row>
-    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E81" s="1"/>
-    </row>
-    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E82" s="1"/>
-    </row>
-    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E83" s="1"/>
-    </row>
-    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E84" s="1"/>
-    </row>
-    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E85" s="1"/>
+      <c r="B82" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C82" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D82" s="0" t="n">
+        <v>100</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2214,10 +2076,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Constant.xlsx
+++ b/Constant.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="112">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -114,310 +114,244 @@
     <t xml:space="preserve">USInt</t>
   </si>
   <si>
+    <t xml:space="preserve">CMD_GATE_OPEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMD_NONE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMD_RELEASE_OWNER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMD_RESET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMD_SET_FORCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMD_START</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMD_STOP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLT_ALIGNMENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UInt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLT_BOTH_SENSORS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLT_BREAKER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLT_GATE_MOVE_TIMEOUT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLT_GATE_POS_UNKNOWN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLT_INTERLOCK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLT_NO_FEEDBACK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLT_NO_RUNFB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLT_NONE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLT_OVERFLOW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIMITS_MAX_ROUTES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIMITS_MAX_STEPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAN_REJ_ARBITER_FAIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAN_REJ_CMD_INVALID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAN_REJ_LOCAL_MANUAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAN_REJ_NOT_IDLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAN_REJ_OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAN_REJ_OWNER_BUSY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAN_REJ_SLOT_UNMAPPED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OWNER_NONE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OWNER_ROUTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OWNER_SCADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUTE_ABRT_BY_FAULT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUTE_ABRT_BY_LOCAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUTE_ABRT_BY_OPERATOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUTE_ABRT_BY_OWNER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUTE_ABRT_BY_SAFETY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUTE_OK_RUNNING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUTE_REJ_BY_CONTRACT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUTE_REJ_BY_OWNER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUTE_REJ_BY_SAFETY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUTE_REJ_DUPLICATE_START</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUTE_REJ_NOT_READY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUTE_STS_ABORTED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUTE_STS_IDLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUTE_STS_LOCKING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUTE_STS_REJECTED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUTE_STS_RUNNING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUTE_STS_STARTING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUTE_STS_STOPPING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUTE_STS_VALIDATING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RS_ACT_START</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RS_ACT_STOP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RS_WAIT_RUNNING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RS_WAIT_STOPPED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RT_CMD_NONE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RT_CMD_START</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RT_CMD_STOP_OP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STEP_STS_IDLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STEP_STS_WORK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STS_DISABLED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STS_FAULT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STS_IDLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STS_LOCAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STS_RUNNING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STS_STARTING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STS_STOPPING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TimeoutMs_Fan_Feedback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TimeoutMs_Gate_Move</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TimeoutMs_Gate_Position_Unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TimeoutMs_Noria_SpeedPause</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TimeoutMs_Noria_Start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TimeoutMs_Redler_SpeedPause</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TimeoutMs_Redler_Start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TYPE_FAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TYPE_GATE2P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TYPE_NONE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TYPE_NORIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TYPE_REDLER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TYPE_VALVE3P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
     <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CMD_GATE_OPEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CMD_NONE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CMD_RELEASE_OWNER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CMD_RESET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CMD_SET_FORCE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CMD_START</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CMD_STOP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLT_ALINGMENT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UInt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLT_BOTH_SENSORS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLT_BREAKER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLT_GATE_MOVE_TIMEOUT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLT_GATE_POS_UNKNOWN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLT_INTERLOCK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLT_NO_FEEDBACK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLT_NO_RUNFB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLT_NONE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLT_OVERFLOW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIMITS_MAX_ROUTES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIMITS_MAX_STEPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAN_REJ_ARBITER_FAIL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAN_REJ_CMD_INVALID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAN_REJ_LOCAL_MANUAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAN_REJ_NOT_ENABLED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAN_REJ_NOT_IDLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAN_REJ_OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAN_REJ_OWNER_BUSY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAN_REJ_SLOT_UNMAPPED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OWNER_NONE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OWNER_ROUTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OWNER_SCADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUTE_ABRT_BY_FAULT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUTE_ABRT_BY_LOCAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUTE_ABRT_BY_OPERATOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUTE_ABRT_BY_OWNER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUTE_ABRT_BY_SAFETY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUTE_DONE_OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUTE_REJ_BY_CONTRACT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUTE_REJ_BY_OWNER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUTE_REJ_BY_SAFETY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUTE_REJ_DUPLICATE_START</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUTE_REJ_NOT_READY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUTE_STS_ABORTED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUTE_STS_DONE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUTE_STS_IDLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUTE_STS_LOCKING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUTE_STS_REJECTED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUTE_STS_RUNNING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUTE_STS_STARTING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUTE_STS_STOPPING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUTE_STS_VALIDATING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RS_ACT_START</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RS_ACT_STOP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RS_WAIT_RUNNING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RS_WAIT_STOPPED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RT_CMD_NONE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RT_CMD_START</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RT_CMD_STOP_OP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STEP_STS_DONE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STEP_STS_IDLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STEP_STS_WORK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STS_DISABLED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STS_FAULT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STS_IDLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STS_LOCAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STS_RUNNING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STS_STARTING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STS_STOPPING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TimeoutMs_Fan_Feedback</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TimeoutMs_Gate_Move</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TimeoutMs_Gate_Position_Unknown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TimeoutMs_Noria_SpeedPause</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TimeoutMs_Noria_Start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TimeoutMs_Redler_SpeedPause</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TimeoutMs_Redler_Start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TYPE_FAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TYPE_GATE2P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TYPE_NONE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TYPE_NORIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TYPE_REDLER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TYPE_VALVE3P</t>
   </si>
   <si>
     <t xml:space="preserve">BelongsToUnit</t>
@@ -501,7 +435,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -514,6 +448,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -523,15 +465,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -857,7 +790,7 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="35.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="26.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="26.89"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -887,14 +820,14 @@
       <c r="C2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>30</v>
+      <c r="D2" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="E2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>11</v>
@@ -902,14 +835,14 @@
       <c r="C3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>32</v>
+      <c r="D3" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="E3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>11</v>
@@ -917,14 +850,14 @@
       <c r="C4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>34</v>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>11</v>
@@ -932,14 +865,14 @@
       <c r="C5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>30</v>
+      <c r="D5" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="E5" s="1"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>11</v>
@@ -947,14 +880,14 @@
       <c r="C6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>37</v>
+      <c r="D6" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="E6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>11</v>
@@ -962,14 +895,14 @@
       <c r="C7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>32</v>
+      <c r="D7" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="E7" s="1"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -977,14 +910,14 @@
       <c r="C8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>40</v>
+      <c r="D8" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>11</v>
@@ -992,164 +925,164 @@
       <c r="C9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>42</v>
+      <c r="D9" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="E9" s="1"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="E10" s="1"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="E11" s="1"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>49</v>
+        <v>38</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="E12" s="1"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>51</v>
+        <v>38</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>16</v>
       </c>
       <c r="E13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>53</v>
+        <v>38</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="E14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="E15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>57</v>
+        <v>38</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>14</v>
       </c>
       <c r="E16" s="1"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>59</v>
+        <v>38</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="E17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E18" s="1"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>62</v>
+        <v>38</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="E19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>11</v>
@@ -1157,29 +1090,29 @@
       <c r="C20" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>59</v>
+      <c r="D20" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="E20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="3" t="n">
         <v>64</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="E21" s="1"/>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>11</v>
@@ -1187,14 +1120,14 @@
       <c r="C22" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>67</v>
+      <c r="D22" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="E22" s="1"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>11</v>
@@ -1202,14 +1135,14 @@
       <c r="C23" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>30</v>
+      <c r="D23" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="E23" s="1"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>11</v>
@@ -1217,14 +1150,14 @@
       <c r="C24" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>42</v>
+      <c r="D24" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="E24" s="1"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>11</v>
@@ -1232,14 +1165,14 @@
       <c r="C25" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>37</v>
+      <c r="D25" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="E25" s="1"/>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>11</v>
@@ -1247,14 +1180,14 @@
       <c r="C26" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>72</v>
+      <c r="D26" s="3" t="n">
+        <v>7</v>
       </c>
       <c r="E26" s="1"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>11</v>
@@ -1262,14 +1195,14 @@
       <c r="C27" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>34</v>
+      <c r="D27" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E27" s="1"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>11</v>
@@ -1277,14 +1210,14 @@
       <c r="C28" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>32</v>
+      <c r="D28" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="E28" s="1"/>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>11</v>
@@ -1292,14 +1225,14 @@
       <c r="C29" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>40</v>
+      <c r="D29" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E29" s="1"/>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>11</v>
@@ -1307,14 +1240,14 @@
       <c r="C30" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>34</v>
+      <c r="D30" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E30" s="1"/>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>11</v>
@@ -1322,14 +1255,14 @@
       <c r="C31" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>42</v>
+      <c r="D31" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="E31" s="1"/>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>11</v>
@@ -1337,314 +1270,314 @@
       <c r="C32" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>40</v>
+      <c r="D32" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E32" s="1"/>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D33" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="D33" s="4" t="n">
         <v>252</v>
       </c>
       <c r="E33" s="1"/>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D34" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="D34" s="4" t="n">
         <v>251</v>
       </c>
       <c r="E34" s="1"/>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D35" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="D35" s="4" t="n">
         <v>250</v>
       </c>
       <c r="E35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D36" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="D36" s="4" t="n">
         <v>254</v>
       </c>
       <c r="E36" s="1"/>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D37" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="D37" s="4" t="n">
         <v>253</v>
       </c>
       <c r="E37" s="1"/>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="D38" s="4" t="n">
         <v>200</v>
       </c>
       <c r="E38" s="1"/>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D39" s="2" t="n">
-        <v>200</v>
+        <v>38</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>205</v>
       </c>
       <c r="E39" s="1"/>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D40" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="D40" s="4" t="n">
         <v>201</v>
       </c>
       <c r="E40" s="1"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D41" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="D41" s="4" t="n">
         <v>204</v>
       </c>
       <c r="E41" s="1"/>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D42" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="D42" s="4" t="n">
         <v>203</v>
       </c>
       <c r="E42" s="1"/>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D43" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="D43" s="4" t="n">
         <v>202</v>
       </c>
       <c r="E43" s="1"/>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D44" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="D44" s="4" t="n">
         <v>8</v>
       </c>
       <c r="E44" s="1"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D45" s="2" t="n">
-        <v>6</v>
+        <v>38</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E45" s="1"/>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D46" s="2" t="n">
-        <v>0</v>
+        <v>38</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>2</v>
       </c>
       <c r="E46" s="1"/>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D47" s="2" t="n">
-        <v>2</v>
+        <v>38</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>7</v>
       </c>
       <c r="E47" s="1"/>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D48" s="2" t="n">
-        <v>7</v>
+        <v>38</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>4</v>
       </c>
       <c r="E48" s="1"/>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D49" s="2" t="n">
-        <v>4</v>
+        <v>38</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>3</v>
       </c>
       <c r="E49" s="1"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D50" s="2" t="n">
-        <v>3</v>
+        <v>38</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>5</v>
       </c>
       <c r="E50" s="1"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D51" s="2" t="n">
-        <v>5</v>
+        <v>38</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="E51" s="1"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D52" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="D52" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E52" s="1"/>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>11</v>
@@ -1652,13 +1585,13 @@
       <c r="C53" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D53" s="2" t="n">
-        <v>1</v>
+      <c r="D53" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>11</v>
@@ -1666,13 +1599,13 @@
       <c r="C54" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D54" s="2" t="n">
-        <v>2</v>
+      <c r="D54" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>11</v>
@@ -1680,13 +1613,13 @@
       <c r="C55" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D55" s="2" t="n">
-        <v>1</v>
+      <c r="D55" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>11</v>
@@ -1694,13 +1627,13 @@
       <c r="C56" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D56" s="2" t="n">
-        <v>2</v>
+      <c r="D56" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>11</v>
@@ -1708,13 +1641,13 @@
       <c r="C57" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D57" s="2" t="n">
-        <v>0</v>
+      <c r="D57" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>11</v>
@@ -1722,13 +1655,13 @@
       <c r="C58" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D58" s="2" t="n">
-        <v>1</v>
+      <c r="D58" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>11</v>
@@ -1736,13 +1669,13 @@
       <c r="C59" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D59" s="2" t="n">
-        <v>2</v>
+      <c r="D59" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>11</v>
@@ -1750,139 +1683,139 @@
       <c r="C60" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D60" s="2" t="n">
-        <v>2</v>
+      <c r="D60" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D61" s="2" t="n">
-        <v>0</v>
+        <v>38</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D62" s="2" t="n">
-        <v>1</v>
+        <v>38</v>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>62</v>
+        <v>38</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>49</v>
+        <v>38</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>40</v>
+        <v>25</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>5000</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>37</v>
+        <v>25</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>10000</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>11</v>
@@ -1890,13 +1823,13 @@
       <c r="C70" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D70" s="1" t="s">
-        <v>117</v>
+      <c r="D70" s="3" t="n">
+        <v>10000</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>11</v>
@@ -1904,13 +1837,13 @@
       <c r="C71" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D71" s="1" t="s">
-        <v>119</v>
+      <c r="D71" s="3" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>11</v>
@@ -1918,13 +1851,13 @@
       <c r="C72" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D72" s="1" t="s">
-        <v>119</v>
+      <c r="D72" s="3" t="n">
+        <v>5000</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>11</v>
@@ -1932,13 +1865,13 @@
       <c r="C73" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D73" s="1" t="s">
-        <v>122</v>
+      <c r="D73" s="3" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>11</v>
@@ -1946,41 +1879,41 @@
       <c r="C74" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D74" s="1" t="s">
-        <v>117</v>
+      <c r="D74" s="3" t="n">
+        <v>5000</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>122</v>
+        <v>29</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>117</v>
+        <v>29</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>11</v>
@@ -1988,13 +1921,13 @@
       <c r="C77" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D77" s="1" t="s">
-        <v>32</v>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>11</v>
@@ -2002,13 +1935,13 @@
       <c r="C78" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D78" s="1" t="s">
-        <v>37</v>
+      <c r="D78" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>11</v>
@@ -2016,13 +1949,13 @@
       <c r="C79" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D79" s="1" t="s">
-        <v>34</v>
+      <c r="D79" s="3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>11</v>
@@ -2030,13 +1963,13 @@
       <c r="C80" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D80" s="1" t="s">
-        <v>40</v>
+      <c r="D80" s="3" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>11</v>
@@ -2044,13 +1977,13 @@
       <c r="C81" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D81" s="1" t="s">
-        <v>42</v>
+      <c r="D81" s="3" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>11</v>
@@ -2058,8 +1991,8 @@
       <c r="C82" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D82" s="1" t="s">
-        <v>30</v>
+      <c r="D82" s="3" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -2089,10 +2022,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Constant.xlsx
+++ b/Constant.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="172">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -86,16 +86,16 @@
     <t xml:space="preserve">Неправильний статус для команди — не IDLE і не FAULT</t>
   </si>
   <si>
-    <t xml:space="preserve">CMD_GATE_CLOSED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Команда засувці — закрити</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CMD_GATE_OPEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Команда засувці — відкрити</t>
+    <t xml:space="preserve">CMD_GATE_POS0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Команда засувці — перейти в положення 0 (закрито)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMD_GATE_POS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Команда засувці — перейти в положення 1 (відкрито)</t>
   </si>
   <si>
     <t xml:space="preserve">CMD_NONE</t>
@@ -167,22 +167,10 @@
     <t xml:space="preserve">Невідома позиція засувки після переміщення</t>
   </si>
   <si>
-    <t xml:space="preserve">FLT_INTERLOCK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Аварія блокування (інтерлок)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLT_NO_FEEDBACK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Немає зворотного зв'язку</t>
-  </si>
-  <si>
     <t xml:space="preserve">FLT_NO_RUNFB</t>
   </si>
   <si>
-    <t xml:space="preserve">Немає зворотного зв'язку роботи (редлер/норія)</t>
+    <t xml:space="preserve">Немає зворотного зв'язку роботи (норія/редлер/вентилятор)</t>
   </si>
   <si>
     <t xml:space="preserve">FLT_NONE</t>
@@ -1143,7 +1131,7 @@
         <v>38</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E22" s="0" t="s">
         <v>49</v>
@@ -1160,7 +1148,7 @@
         <v>38</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E23" s="0" t="s">
         <v>51</v>
@@ -1177,7 +1165,7 @@
         <v>38</v>
       </c>
       <c r="D24" s="0" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E24" s="0" t="s">
         <v>53</v>
@@ -1191,10 +1179,10 @@
         <v>6</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E25" s="0" t="s">
         <v>55</v>
@@ -1208,10 +1196,10 @@
         <v>6</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="D26" s="0" t="n">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="E26" s="0" t="s">
         <v>57</v>
@@ -1228,7 +1216,7 @@
         <v>7</v>
       </c>
       <c r="D27" s="0" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E27" s="0" t="s">
         <v>59</v>
@@ -1245,7 +1233,7 @@
         <v>7</v>
       </c>
       <c r="D28" s="0" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="E28" s="0" t="s">
         <v>61</v>
@@ -1262,7 +1250,7 @@
         <v>7</v>
       </c>
       <c r="D29" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="0" t="s">
         <v>63</v>
@@ -1276,10 +1264,10 @@
         <v>6</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D30" s="0" t="n">
-        <v>2</v>
+        <v>304</v>
       </c>
       <c r="E30" s="0" t="s">
         <v>65</v>
@@ -1293,10 +1281,10 @@
         <v>6</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D31" s="0" t="n">
-        <v>1</v>
+        <v>303</v>
       </c>
       <c r="E31" s="0" t="s">
         <v>67</v>
@@ -1313,7 +1301,7 @@
         <v>38</v>
       </c>
       <c r="D32" s="0" t="n">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E32" s="0" t="s">
         <v>69</v>
@@ -1330,7 +1318,7 @@
         <v>38</v>
       </c>
       <c r="D33" s="0" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E33" s="0" t="s">
         <v>71</v>
@@ -1347,7 +1335,7 @@
         <v>38</v>
       </c>
       <c r="D34" s="0" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E34" s="0" t="s">
         <v>73</v>
@@ -1364,7 +1352,7 @@
         <v>38</v>
       </c>
       <c r="D35" s="0" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E35" s="0" t="s">
         <v>75</v>
@@ -1381,7 +1369,7 @@
         <v>38</v>
       </c>
       <c r="D36" s="0" t="n">
-        <v>302</v>
+        <v>200</v>
       </c>
       <c r="E36" s="0" t="s">
         <v>77</v>
@@ -1398,7 +1386,7 @@
         <v>38</v>
       </c>
       <c r="D37" s="0" t="n">
-        <v>306</v>
+        <v>203</v>
       </c>
       <c r="E37" s="0" t="s">
         <v>79</v>
@@ -1415,7 +1403,7 @@
         <v>38</v>
       </c>
       <c r="D38" s="0" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E38" s="0" t="s">
         <v>81</v>
@@ -1432,7 +1420,7 @@
         <v>38</v>
       </c>
       <c r="D39" s="0" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E39" s="0" t="s">
         <v>83</v>
@@ -1449,7 +1437,7 @@
         <v>38</v>
       </c>
       <c r="D40" s="0" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E40" s="0" t="s">
         <v>85</v>
@@ -1466,7 +1454,7 @@
         <v>38</v>
       </c>
       <c r="D41" s="0" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E41" s="0" t="s">
         <v>87</v>
@@ -1483,7 +1471,7 @@
         <v>38</v>
       </c>
       <c r="D42" s="0" t="n">
-        <v>205</v>
+        <v>8</v>
       </c>
       <c r="E42" s="0" t="s">
         <v>89</v>
@@ -1500,7 +1488,7 @@
         <v>38</v>
       </c>
       <c r="D43" s="0" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="E43" s="0" t="s">
         <v>91</v>
@@ -1517,7 +1505,7 @@
         <v>38</v>
       </c>
       <c r="D44" s="0" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E44" s="0" t="s">
         <v>93</v>
@@ -1534,7 +1522,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="0" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E45" s="0" t="s">
         <v>95</v>
@@ -1551,7 +1539,7 @@
         <v>38</v>
       </c>
       <c r="D46" s="0" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E46" s="0" t="s">
         <v>97</v>
@@ -1568,7 +1556,7 @@
         <v>38</v>
       </c>
       <c r="D47" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E47" s="0" t="s">
         <v>99</v>
@@ -1585,7 +1573,7 @@
         <v>38</v>
       </c>
       <c r="D48" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48" s="0" t="s">
         <v>101</v>
@@ -1599,10 +1587,10 @@
         <v>6</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="D49" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E49" s="0" t="s">
         <v>103</v>
@@ -1616,10 +1604,10 @@
         <v>6</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="D50" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" s="0" t="s">
         <v>105</v>
@@ -1687,7 +1675,7 @@
         <v>7</v>
       </c>
       <c r="D54" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E54" s="0" t="s">
         <v>113</v>
@@ -1704,7 +1692,7 @@
         <v>7</v>
       </c>
       <c r="D55" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" s="0" t="s">
         <v>115</v>
@@ -1721,7 +1709,7 @@
         <v>7</v>
       </c>
       <c r="D56" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" s="0" t="s">
         <v>117</v>
@@ -1738,7 +1726,7 @@
         <v>7</v>
       </c>
       <c r="D57" s="0" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E57" s="0" t="s">
         <v>119</v>
@@ -1755,7 +1743,7 @@
         <v>7</v>
       </c>
       <c r="D58" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E58" s="0" t="s">
         <v>121</v>
@@ -1789,7 +1777,7 @@
         <v>7</v>
       </c>
       <c r="D60" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E60" s="0" t="s">
         <v>125</v>
@@ -1806,7 +1794,7 @@
         <v>7</v>
       </c>
       <c r="D61" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E61" s="0" t="s">
         <v>127</v>
@@ -1823,7 +1811,7 @@
         <v>7</v>
       </c>
       <c r="D62" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E62" s="0" t="s">
         <v>129</v>
@@ -1837,10 +1825,10 @@
         <v>6</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D63" s="0" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E63" s="0" t="s">
         <v>131</v>
@@ -1854,10 +1842,10 @@
         <v>6</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D64" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E64" s="0" t="s">
         <v>133</v>
@@ -1874,7 +1862,7 @@
         <v>38</v>
       </c>
       <c r="D65" s="0" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E65" s="0" t="s">
         <v>135</v>
@@ -1891,44 +1879,44 @@
         <v>38</v>
       </c>
       <c r="D66" s="0" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E66" s="0" t="s">
-        <v>137</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="B67" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="D67" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E67" s="0" t="s">
         <v>138</v>
-      </c>
-      <c r="B67" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C67" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="D67" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" s="0" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="B68" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="D68" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="0" t="s">
         <v>140</v>
-      </c>
-      <c r="B68" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C68" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="D68" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="E68" s="0" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1942,7 +1930,7 @@
         <v>38</v>
       </c>
       <c r="D69" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E69" s="0" t="s">
         <v>142</v>
@@ -1956,44 +1944,44 @@
         <v>6</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>38</v>
+        <v>144</v>
       </c>
       <c r="D70" s="0" t="n">
-        <v>1</v>
+        <v>5000</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B71" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>38</v>
+        <v>144</v>
       </c>
       <c r="D71" s="0" t="n">
-        <v>3</v>
+        <v>10000</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B72" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D72" s="0" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="E72" s="0" t="s">
         <v>149</v>
@@ -2007,10 +1995,10 @@
         <v>6</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D73" s="0" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="E73" s="0" t="s">
         <v>151</v>
@@ -2024,10 +2012,10 @@
         <v>6</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D74" s="0" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="E74" s="0" t="s">
         <v>153</v>
@@ -2041,7 +2029,7 @@
         <v>6</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D75" s="0" t="n">
         <v>2000</v>
@@ -2058,7 +2046,7 @@
         <v>6</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D76" s="0" t="n">
         <v>5000</v>
@@ -2075,10 +2063,10 @@
         <v>6</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>148</v>
+        <v>7</v>
       </c>
       <c r="D77" s="0" t="n">
-        <v>2000</v>
+        <v>4</v>
       </c>
       <c r="E77" s="0" t="s">
         <v>159</v>
@@ -2092,10 +2080,10 @@
         <v>6</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>148</v>
+        <v>7</v>
       </c>
       <c r="D78" s="0" t="n">
-        <v>5000</v>
+        <v>3</v>
       </c>
       <c r="E78" s="0" t="s">
         <v>161</v>
@@ -2112,7 +2100,7 @@
         <v>7</v>
       </c>
       <c r="D79" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E79" s="0" t="s">
         <v>163</v>
@@ -2129,7 +2117,7 @@
         <v>7</v>
       </c>
       <c r="D80" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E80" s="0" t="s">
         <v>165</v>
@@ -2146,7 +2134,7 @@
         <v>7</v>
       </c>
       <c r="D81" s="0" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E81" s="0" t="s">
         <v>167</v>
@@ -2163,62 +2151,26 @@
         <v>7</v>
       </c>
       <c r="D82" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E82" s="0" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="B83" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C83" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="D83" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="E83" s="0" t="s">
-        <v>171</v>
-      </c>
+      <c r="B83" s="1"/>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="s">
-        <v>172</v>
-      </c>
-      <c r="B84" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C84" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="D84" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="E84" s="0" t="s">
-        <v>173</v>
-      </c>
+      <c r="B84" s="1"/>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B85" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C85" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="D85" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="E85" s="0" t="s">
-        <v>8</v>
-      </c>
+      <c r="B85" s="1"/>
+      <c r="C85" s="1"/>
+      <c r="D85" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2244,10 +2196,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Constant.xlsx
+++ b/Constant.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="180">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -185,6 +185,21 @@
     <t xml:space="preserve">Аварія переповнення</t>
   </si>
   <si>
+    <t xml:space="preserve">GATE_AT_POS0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status_Param засувки — знаходиться в положенні 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GATE_AT_POS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status_Param засувки — знаходиться в положенні 1</t>
+  </si>
+  <si>
     <t xml:space="preserve">LIMITS_MAX_ROUTES</t>
   </si>
   <si>
@@ -531,6 +546,15 @@
   </si>
   <si>
     <t xml:space="preserve">Тип механізму — клапан трипозиційний</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUTES_COUNT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кількість паралельних маршрутів</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUTE_MAX_STEPS</t>
   </si>
   <si>
     <t xml:space="preserve">BelongsToUnit</t>
@@ -754,7 +778,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.19"/>
@@ -1179,35 +1203,35 @@
         <v>6</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="D26" s="0" t="n">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B27" s="0" t="s">
         <v>6</v>
@@ -1216,15 +1240,15 @@
         <v>7</v>
       </c>
       <c r="D27" s="0" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B28" s="0" t="s">
         <v>6</v>
@@ -1233,15 +1257,15 @@
         <v>7</v>
       </c>
       <c r="D28" s="0" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B29" s="0" t="s">
         <v>6</v>
@@ -1250,49 +1274,49 @@
         <v>7</v>
       </c>
       <c r="D29" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B30" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="D30" s="0" t="n">
-        <v>304</v>
+        <v>2</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B31" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="D31" s="0" t="n">
-        <v>303</v>
+        <v>1</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B32" s="0" t="s">
         <v>6</v>
@@ -1301,15 +1325,15 @@
         <v>38</v>
       </c>
       <c r="D32" s="0" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B33" s="0" t="s">
         <v>6</v>
@@ -1318,15 +1342,15 @@
         <v>38</v>
       </c>
       <c r="D33" s="0" t="n">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B34" s="0" t="s">
         <v>6</v>
@@ -1335,15 +1359,15 @@
         <v>38</v>
       </c>
       <c r="D34" s="0" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E34" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B35" s="0" t="s">
         <v>6</v>
@@ -1352,15 +1376,15 @@
         <v>38</v>
       </c>
       <c r="D35" s="0" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B36" s="0" t="s">
         <v>6</v>
@@ -1369,15 +1393,15 @@
         <v>38</v>
       </c>
       <c r="D36" s="0" t="n">
-        <v>200</v>
+        <v>302</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B37" s="0" t="s">
         <v>6</v>
@@ -1386,15 +1410,15 @@
         <v>38</v>
       </c>
       <c r="D37" s="0" t="n">
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B38" s="0" t="s">
         <v>6</v>
@@ -1403,15 +1427,15 @@
         <v>38</v>
       </c>
       <c r="D38" s="0" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B39" s="0" t="s">
         <v>6</v>
@@ -1420,15 +1444,15 @@
         <v>38</v>
       </c>
       <c r="D39" s="0" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B40" s="0" t="s">
         <v>6</v>
@@ -1437,15 +1461,15 @@
         <v>38</v>
       </c>
       <c r="D40" s="0" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B41" s="0" t="s">
         <v>6</v>
@@ -1454,15 +1478,15 @@
         <v>38</v>
       </c>
       <c r="D41" s="0" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B42" s="0" t="s">
         <v>6</v>
@@ -1471,15 +1495,15 @@
         <v>38</v>
       </c>
       <c r="D42" s="0" t="n">
-        <v>8</v>
+        <v>205</v>
       </c>
       <c r="E42" s="0" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B43" s="0" t="s">
         <v>6</v>
@@ -1488,15 +1512,15 @@
         <v>38</v>
       </c>
       <c r="D43" s="0" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B44" s="0" t="s">
         <v>6</v>
@@ -1505,15 +1529,15 @@
         <v>38</v>
       </c>
       <c r="D44" s="0" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B45" s="0" t="s">
         <v>6</v>
@@ -1522,15 +1546,15 @@
         <v>38</v>
       </c>
       <c r="D45" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B46" s="0" t="s">
         <v>6</v>
@@ -1539,15 +1563,15 @@
         <v>38</v>
       </c>
       <c r="D46" s="0" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B47" s="0" t="s">
         <v>6</v>
@@ -1556,15 +1580,15 @@
         <v>38</v>
       </c>
       <c r="D47" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E47" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B48" s="0" t="s">
         <v>6</v>
@@ -1573,49 +1597,49 @@
         <v>38</v>
       </c>
       <c r="D48" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B49" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D49" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B50" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D50" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B51" s="0" t="s">
         <v>6</v>
@@ -1627,12 +1651,12 @@
         <v>1</v>
       </c>
       <c r="E51" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B52" s="0" t="s">
         <v>6</v>
@@ -1644,12 +1668,12 @@
         <v>2</v>
       </c>
       <c r="E52" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B53" s="0" t="s">
         <v>6</v>
@@ -1661,12 +1685,12 @@
         <v>1</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B54" s="0" t="s">
         <v>6</v>
@@ -1675,15 +1699,15 @@
         <v>7</v>
       </c>
       <c r="D54" s="0" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B55" s="0" t="s">
         <v>6</v>
@@ -1692,15 +1716,15 @@
         <v>7</v>
       </c>
       <c r="D55" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B56" s="0" t="s">
         <v>6</v>
@@ -1709,15 +1733,15 @@
         <v>7</v>
       </c>
       <c r="D56" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B57" s="0" t="s">
         <v>6</v>
@@ -1726,15 +1750,15 @@
         <v>7</v>
       </c>
       <c r="D57" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B58" s="0" t="s">
         <v>6</v>
@@ -1743,15 +1767,15 @@
         <v>7</v>
       </c>
       <c r="D58" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B59" s="0" t="s">
         <v>6</v>
@@ -1763,12 +1787,12 @@
         <v>2</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B60" s="0" t="s">
         <v>6</v>
@@ -1777,15 +1801,15 @@
         <v>7</v>
       </c>
       <c r="D60" s="0" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E60" s="0" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B61" s="0" t="s">
         <v>6</v>
@@ -1794,15 +1818,15 @@
         <v>7</v>
       </c>
       <c r="D61" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B62" s="0" t="s">
         <v>6</v>
@@ -1811,49 +1835,49 @@
         <v>7</v>
       </c>
       <c r="D62" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B63" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="D63" s="0" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B64" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="D64" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B65" s="0" t="s">
         <v>6</v>
@@ -1862,15 +1886,15 @@
         <v>38</v>
       </c>
       <c r="D65" s="0" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B66" s="0" t="s">
         <v>6</v>
@@ -1879,15 +1903,15 @@
         <v>38</v>
       </c>
       <c r="D66" s="0" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E66" s="0" t="s">
-        <v>12</v>
+        <v>138</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B67" s="0" t="s">
         <v>6</v>
@@ -1896,15 +1920,15 @@
         <v>38</v>
       </c>
       <c r="D67" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B68" s="0" t="s">
         <v>6</v>
@@ -1913,15 +1937,15 @@
         <v>38</v>
       </c>
       <c r="D68" s="0" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E68" s="0" t="s">
-        <v>140</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B69" s="0" t="s">
         <v>6</v>
@@ -1930,24 +1954,24 @@
         <v>38</v>
       </c>
       <c r="D69" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B70" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>144</v>
+        <v>38</v>
       </c>
       <c r="D70" s="0" t="n">
-        <v>5000</v>
+        <v>1</v>
       </c>
       <c r="E70" s="0" t="s">
         <v>145</v>
@@ -1961,10 +1985,10 @@
         <v>6</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>144</v>
+        <v>38</v>
       </c>
       <c r="D71" s="0" t="n">
-        <v>10000</v>
+        <v>3</v>
       </c>
       <c r="E71" s="0" t="s">
         <v>147</v>
@@ -1978,120 +2002,120 @@
         <v>6</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D72" s="0" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B73" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D73" s="0" t="n">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="E73" s="0" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B74" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D74" s="0" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="E74" s="0" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B75" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D75" s="0" t="n">
         <v>2000</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B76" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D76" s="0" t="n">
         <v>5000</v>
       </c>
       <c r="E76" s="0" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B77" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>7</v>
+        <v>149</v>
       </c>
       <c r="D77" s="0" t="n">
-        <v>4</v>
+        <v>2000</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B78" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>7</v>
+        <v>149</v>
       </c>
       <c r="D78" s="0" t="n">
-        <v>3</v>
+        <v>5000</v>
       </c>
       <c r="E78" s="0" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B79" s="0" t="s">
         <v>6</v>
@@ -2100,15 +2124,15 @@
         <v>7</v>
       </c>
       <c r="D79" s="0" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B80" s="0" t="s">
         <v>6</v>
@@ -2117,15 +2141,15 @@
         <v>7</v>
       </c>
       <c r="D80" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E80" s="0" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B81" s="0" t="s">
         <v>6</v>
@@ -2134,15 +2158,15 @@
         <v>7</v>
       </c>
       <c r="D81" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B82" s="0" t="s">
         <v>6</v>
@@ -2151,26 +2175,79 @@
         <v>7</v>
       </c>
       <c r="D82" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="0" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="0" t="s">
+        <v>171</v>
+      </c>
+      <c r="B83" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="D83" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E83" s="0" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="B84" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="D84" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="E82" s="0" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B83" s="1"/>
-      <c r="C83" s="1"/>
-      <c r="D83" s="1"/>
-    </row>
-    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="1"/>
-      <c r="C84" s="1"/>
-      <c r="D84" s="1"/>
+      <c r="E84" s="0" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B85" s="1"/>
-      <c r="C85" s="1"/>
-      <c r="D85" s="1"/>
+      <c r="A85" s="0" t="s">
+        <v>175</v>
+      </c>
+      <c r="B85" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="D85" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="E85" s="0" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="0" t="s">
+        <v>177</v>
+      </c>
+      <c r="B86" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="D86" s="0" t="n">
+        <v>64</v>
+      </c>
+      <c r="E86" s="0" t="s">
+        <v>62</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2196,10 +2273,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Constant.xlsx
+++ b/Constant.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="263">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -133,67 +133,91 @@
     <t xml:space="preserve">Зупинити механізм</t>
   </si>
   <si>
+    <t xml:space="preserve">FLT_NONE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Word</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Немає аварії</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLT_BREAKER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Аварія автомата захисту (BIT0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLT_OVERFLOW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Аварія переповнення (BIT1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLT_NO_RUNFB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Немає зворотного зв'язку роботи тахо (BIT2)</t>
+  </si>
+  <si>
     <t xml:space="preserve">FLT_ALINGMENT</t>
   </si>
   <si>
-    <t xml:space="preserve">Word</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Аварія вирівнювання (норія)</t>
+    <t xml:space="preserve">Аварія вирівнювання норія (BIT3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLT_NO_FEEDBACK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Немає зворотного зв'язку контактора (BIT4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLT_GATE_MOVE_TIMEOUT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Таймаут переміщення засувки (BIT5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLT_GATE_POS_UNKNOWN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Невідома позиція засувки після переміщення (BIT6)</t>
   </si>
   <si>
     <t xml:space="preserve">FLT_BOTH_SENSORS</t>
   </si>
   <si>
-    <t xml:space="preserve">Обидва кінцеві датчики активні одночасно (засувка)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLT_BREAKER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Аварія автомата захисту</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLT_GATE_MOVE_TIMEOUT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Таймаут переміщення засувки</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLT_GATE_POS_UNKNOWN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Невідома позиція засувки після переміщення</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLT_NO_FEEDBACK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Немає зворотного зв'язку контактора (редлер/норія/вентилятор/сепаратор)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLT_NO_RUNFB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Немає зворотного зв'язку роботи (норія/редлер/вентилятор)</t>
+    <t xml:space="preserve">Обидва кінцеві датчики активні одночасно засувка (BIT7)</t>
   </si>
   <si>
     <t xml:space="preserve">FLT_STOP_TIMEOUT</t>
   </si>
   <si>
-    <t xml:space="preserve">Таймаут вибігу при зупинці (редлер/норія/вентилятор/сепаратор/фідер)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLT_NONE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Немає аварії</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLT_OVERFLOW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Аварія переповнення</t>
+    <t xml:space="preserve">Таймаут вибігу при зупинці (BIT8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLT_VALVE_MOVE_TIMEOUT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Таймаут переміщення клапана (BIT9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLT_VALVE_POS_UNKNOWN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Невідома позиція клапана після переміщення (BIT10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLT_VALVE_MULTIPLE_POS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кілька датчиків позиції клапана активні (BIT11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLT_INTERLOCK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Блокування (BIT12)</t>
   </si>
   <si>
     <t xml:space="preserve">GATE_AT_POS0</t>
@@ -739,9 +763,6 @@
     <t xml:space="preserve">ROUTE_MAX_STEPS</t>
   </si>
   <si>
-    <t xml:space="preserve">FLT_INTERLOCK</t>
-  </si>
-  <si>
     <t xml:space="preserve">ROUTE_STS_LOCKING</t>
   </si>
   <si>
@@ -769,18 +790,6 @@
     <t xml:space="preserve">Таймаут невизначеної позиції клапана (мс)</t>
   </si>
   <si>
-    <t xml:space="preserve">FLT_VALVE_MOVE_TIMEOUT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Таймаут переміщення клапана</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLT_VALVE_POS_UNKNOWN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Невідома позиція клапана після переміщення</t>
-  </si>
-  <si>
     <t xml:space="preserve">TYPE_Receiving_PIT</t>
   </si>
   <si>
@@ -800,9 +809,6 @@
   </si>
   <si>
     <t xml:space="preserve">центр</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLT_VALVE_MULTIPLE_POS</t>
   </si>
 </sst>
 </file>
@@ -1012,14 +1018,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E135"/>
+  <dimension ref="A1:E139"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="64.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="56.21"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1305,7 +1311,7 @@
         <v>38</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>39</v>
@@ -1322,7 +1328,7 @@
         <v>38</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>41</v>
@@ -1339,7 +1345,7 @@
         <v>38</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>43</v>
@@ -1356,7 +1362,7 @@
         <v>38</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>45</v>
@@ -1373,7 +1379,7 @@
         <v>38</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>47</v>
@@ -1390,7 +1396,7 @@
         <v>38</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>49</v>
@@ -1407,7 +1413,7 @@
         <v>38</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>51</v>
@@ -1424,7 +1430,7 @@
         <v>38</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>53</v>
@@ -1441,7 +1447,7 @@
         <v>38</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>55</v>
@@ -1458,7 +1464,7 @@
         <v>38</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>10</v>
+        <v>256</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>57</v>
@@ -1472,78 +1478,78 @@
         <v>6</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>512</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>1024</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>2048</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>4096</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="D31" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>68</v>
@@ -1557,10 +1563,10 @@
         <v>6</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>70</v>
@@ -1574,10 +1580,10 @@
         <v>6</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>72</v>
@@ -1591,10 +1597,10 @@
         <v>6</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>74</v>
@@ -1608,10 +1614,10 @@
         <v>6</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>76</v>
@@ -1625,10 +1631,10 @@
         <v>6</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>78</v>
@@ -1645,7 +1651,7 @@
         <v>7</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>80</v>
@@ -1659,78 +1665,78 @@
         <v>6</v>
       </c>
       <c r="C38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="D38" s="1" t="n">
-        <v>304</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D39" s="1" t="n">
-        <v>303</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D40" s="1" t="n">
-        <v>301</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D41" s="1" t="n">
-        <v>305</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="D42" s="1" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>91</v>
@@ -1744,10 +1750,10 @@
         <v>6</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>93</v>
@@ -1761,10 +1767,10 @@
         <v>6</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>95</v>
@@ -1778,10 +1784,10 @@
         <v>6</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>203</v>
+        <v>305</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>97</v>
@@ -1795,10 +1801,10 @@
         <v>6</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>202</v>
+        <v>302</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>99</v>
@@ -1812,10 +1818,10 @@
         <v>6</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>201</v>
+        <v>306</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>101</v>
@@ -1829,10 +1835,10 @@
         <v>6</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>103</v>
@@ -1846,10 +1852,10 @@
         <v>6</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>105</v>
@@ -1863,10 +1869,10 @@
         <v>6</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>107</v>
@@ -1880,10 +1886,10 @@
         <v>6</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>109</v>
@@ -1897,10 +1903,10 @@
         <v>6</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>8</v>
+        <v>205</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>111</v>
@@ -1914,10 +1920,10 @@
         <v>6</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>113</v>
@@ -1931,10 +1937,10 @@
         <v>6</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>7</v>
+        <v>206</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>115</v>
@@ -1948,10 +1954,10 @@
         <v>6</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>4</v>
+        <v>207</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>117</v>
@@ -1965,10 +1971,10 @@
         <v>6</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>119</v>
@@ -1982,10 +1988,10 @@
         <v>6</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>121</v>
@@ -1999,10 +2005,10 @@
         <v>6</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>123</v>
@@ -2016,10 +2022,10 @@
         <v>6</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>125</v>
@@ -2033,7 +2039,7 @@
         <v>6</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="D60" s="1" t="n">
         <v>2</v>
@@ -2050,10 +2056,10 @@
         <v>6</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>129</v>
@@ -2067,10 +2073,10 @@
         <v>6</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>131</v>
@@ -2104,7 +2110,7 @@
         <v>7</v>
       </c>
       <c r="D64" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>135</v>
@@ -2121,7 +2127,7 @@
         <v>7</v>
       </c>
       <c r="D65" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>137</v>
@@ -2138,7 +2144,7 @@
         <v>7</v>
       </c>
       <c r="D66" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>139</v>
@@ -2155,7 +2161,7 @@
         <v>7</v>
       </c>
       <c r="D67" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>141</v>
@@ -2172,7 +2178,7 @@
         <v>7</v>
       </c>
       <c r="D68" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>143</v>
@@ -2189,7 +2195,7 @@
         <v>7</v>
       </c>
       <c r="D69" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>145</v>
@@ -2206,7 +2212,7 @@
         <v>7</v>
       </c>
       <c r="D70" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>147</v>
@@ -2223,7 +2229,7 @@
         <v>7</v>
       </c>
       <c r="D71" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>149</v>
@@ -2240,7 +2246,7 @@
         <v>7</v>
       </c>
       <c r="D72" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>151</v>
@@ -2254,10 +2260,10 @@
         <v>6</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>82</v>
+        <v>7</v>
       </c>
       <c r="D73" s="1" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>153</v>
@@ -2271,10 +2277,10 @@
         <v>6</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>82</v>
+        <v>7</v>
       </c>
       <c r="D74" s="1" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>155</v>
@@ -2288,10 +2294,10 @@
         <v>6</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>82</v>
+        <v>7</v>
       </c>
       <c r="D75" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>157</v>
@@ -2305,146 +2311,146 @@
         <v>6</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>82</v>
+        <v>7</v>
       </c>
       <c r="D76" s="1" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>12</v>
+        <v>159</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D77" s="1" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D78" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D79" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>166</v>
+        <v>90</v>
       </c>
       <c r="D80" s="1" t="n">
-        <v>5000</v>
+        <v>11</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>167</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D81" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E81" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D81" s="1" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D82" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D82" s="1" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D83" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E83" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D83" s="1" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>166</v>
-      </c>
       <c r="D84" s="1" t="n">
-        <v>15000</v>
+        <v>5000</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>175</v>
@@ -2458,7 +2464,7 @@
         <v>6</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D85" s="1" t="n">
         <v>2000</v>
@@ -2475,7 +2481,7 @@
         <v>6</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D86" s="1" t="n">
         <v>10000</v>
@@ -2492,10 +2498,10 @@
         <v>6</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D87" s="1" t="n">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>181</v>
@@ -2509,10 +2515,10 @@
         <v>6</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D88" s="1" t="n">
-        <v>5000</v>
+        <v>15000</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>183</v>
@@ -2526,7 +2532,7 @@
         <v>6</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D89" s="1" t="n">
         <v>2000</v>
@@ -2543,7 +2549,7 @@
         <v>6</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D90" s="1" t="n">
         <v>10000</v>
@@ -2560,7 +2566,7 @@
         <v>6</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D91" s="1" t="n">
         <v>2000</v>
@@ -2577,7 +2583,7 @@
         <v>6</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D92" s="1" t="n">
         <v>5000</v>
@@ -2594,10 +2600,10 @@
         <v>6</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D93" s="1" t="n">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>193</v>
@@ -2611,10 +2617,10 @@
         <v>6</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D94" s="1" t="n">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>195</v>
@@ -2628,10 +2634,10 @@
         <v>6</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D95" s="1" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>197</v>
@@ -2645,7 +2651,7 @@
         <v>6</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D96" s="1" t="n">
         <v>5000</v>
@@ -2662,10 +2668,10 @@
         <v>6</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D97" s="1" t="n">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>201</v>
@@ -2679,10 +2685,10 @@
         <v>6</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D98" s="1" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>203</v>
@@ -2696,10 +2702,10 @@
         <v>6</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D99" s="1" t="n">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>205</v>
@@ -2713,10 +2719,10 @@
         <v>6</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D100" s="1" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>207</v>
@@ -2730,10 +2736,10 @@
         <v>6</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D101" s="1" t="n">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>209</v>
@@ -2747,10 +2753,10 @@
         <v>6</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D102" s="1" t="n">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>211</v>
@@ -2764,7 +2770,7 @@
         <v>6</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D103" s="1" t="n">
         <v>3000</v>
@@ -2781,10 +2787,10 @@
         <v>6</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>7</v>
+        <v>174</v>
       </c>
       <c r="D104" s="1" t="n">
-        <v>4</v>
+        <v>3000</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>215</v>
@@ -2798,10 +2804,10 @@
         <v>6</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>7</v>
+        <v>174</v>
       </c>
       <c r="D105" s="1" t="n">
-        <v>3</v>
+        <v>5000</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>217</v>
@@ -2815,10 +2821,10 @@
         <v>6</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>7</v>
+        <v>174</v>
       </c>
       <c r="D106" s="1" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>219</v>
@@ -2832,10 +2838,10 @@
         <v>6</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>7</v>
+        <v>174</v>
       </c>
       <c r="D107" s="1" t="n">
-        <v>1</v>
+        <v>3000</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>221</v>
@@ -2852,7 +2858,7 @@
         <v>7</v>
       </c>
       <c r="D108" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>223</v>
@@ -2869,7 +2875,7 @@
         <v>7</v>
       </c>
       <c r="D109" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>225</v>
@@ -2886,7 +2892,7 @@
         <v>7</v>
       </c>
       <c r="D110" s="1" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>227</v>
@@ -2903,7 +2909,7 @@
         <v>7</v>
       </c>
       <c r="D111" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>229</v>
@@ -2920,7 +2926,7 @@
         <v>7</v>
       </c>
       <c r="D112" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>231</v>
@@ -2937,7 +2943,7 @@
         <v>7</v>
       </c>
       <c r="D113" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>233</v>
@@ -2954,7 +2960,7 @@
         <v>7</v>
       </c>
       <c r="D114" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>235</v>
@@ -2971,7 +2977,7 @@
         <v>7</v>
       </c>
       <c r="D115" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>237</v>
@@ -2988,43 +2994,49 @@
         <v>7</v>
       </c>
       <c r="D116" s="1" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>74</v>
+        <v>239</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="D117" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>82</v>
+        <v>7</v>
       </c>
       <c r="D118" s="1" t="n">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>6</v>
@@ -3033,15 +3045,15 @@
         <v>7</v>
       </c>
       <c r="D119" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>6</v>
@@ -3050,27 +3062,27 @@
         <v>7</v>
       </c>
       <c r="D120" s="1" t="n">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>244</v>
+        <v>82</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
-        <v>245</v>
+        <v>64</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>166</v>
+        <v>38</v>
       </c>
       <c r="D121" s="1" t="n">
-        <v>15000</v>
+        <v>4096</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>246</v>
+        <v>65</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3081,61 +3093,61 @@
         <v>6</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>166</v>
+        <v>90</v>
       </c>
       <c r="D122" s="1" t="n">
-        <v>15000</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>248</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D123" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="E123" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D123" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D124" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E124" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D124" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D125" s="1" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E125" s="1" t="s">
         <v>253</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D125" s="1" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3146,10 +3158,10 @@
         <v>6</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>7</v>
+        <v>174</v>
       </c>
       <c r="D126" s="1" t="n">
-        <v>3</v>
+        <v>15000</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>255</v>
@@ -3157,79 +3169,119 @@
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
-        <v>256</v>
+        <v>58</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D127" s="1" t="n">
-        <v>4</v>
+        <v>512</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>257</v>
+        <v>59</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
-        <v>258</v>
+        <v>60</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D128" s="1" t="n">
-        <v>5</v>
+        <v>1024</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>259</v>
+        <v>61</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D129" s="1" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D130" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D131" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="E131" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C129" s="1" t="s">
+    </row>
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D132" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C133" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D129" s="1" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="0"/>
-      <c r="B130" s="0"/>
-      <c r="C130" s="0"/>
-      <c r="D130" s="0"/>
-      <c r="E130" s="0"/>
-    </row>
-    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="0"/>
-      <c r="B131" s="0"/>
-      <c r="C131" s="0"/>
-      <c r="D131" s="0"/>
-      <c r="E131" s="0"/>
-    </row>
-    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="0"/>
-      <c r="B132" s="0"/>
-      <c r="C132" s="0"/>
-      <c r="D132" s="0"/>
-      <c r="E132" s="0"/>
-    </row>
-    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="0"/>
-      <c r="B133" s="0"/>
-      <c r="C133" s="0"/>
-      <c r="D133" s="0"/>
-      <c r="E133" s="0"/>
+      <c r="D133" s="1" t="n">
+        <v>2048</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="0"/>
@@ -3244,6 +3296,34 @@
       <c r="C135" s="0"/>
       <c r="D135" s="0"/>
       <c r="E135" s="0"/>
+    </row>
+    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="0"/>
+      <c r="B136" s="0"/>
+      <c r="C136" s="0"/>
+      <c r="D136" s="0"/>
+      <c r="E136" s="0"/>
+    </row>
+    <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="0"/>
+      <c r="B137" s="0"/>
+      <c r="C137" s="0"/>
+      <c r="D137" s="0"/>
+      <c r="E137" s="0"/>
+    </row>
+    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="0"/>
+      <c r="B138" s="0"/>
+      <c r="C138" s="0"/>
+      <c r="D138" s="0"/>
+      <c r="E138" s="0"/>
+    </row>
+    <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="0"/>
+      <c r="B139" s="0"/>
+      <c r="C139" s="0"/>
+      <c r="D139" s="0"/>
+      <c r="E139" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
